--- a/outputs/Заявка №2 в Корею.xlsx
+++ b/outputs/Заявка №2 в Корею.xlsx
@@ -442,16 +442,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G384"/>
+  <dimension ref="A1:I384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,27 +469,37 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Штрихкод</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Количество, шт</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Цена, KRW</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Срок поставки</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Комментарий поставщика</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Коды расходятся</t>
         </is>
       </c>
     </row>
@@ -502,15 +514,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>8809562190738</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Arencia Fresh Green Rice Mochi Cleanser 120g</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -523,15 +541,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>8809562190745</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Arencia Fresh Rosehip Rice Mochi Cleanser 120g</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -544,15 +568,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>8809562192909</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Arencia Blue Hyssop+ Rice Mochi Cleanser 120g</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8809562191070 / 8809562192909</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -565,15 +599,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>8809562191438</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Arencia Calendula Rice Mochi Cleanser 120g</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -586,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>8809562191179</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Arencia Black Tea Rice Mochi Cleanser 120g</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -607,15 +653,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>8809562191629</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Arencia Holy Hyssop Serum 12 30ml</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -628,15 +680,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>8809562190820</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Arencia Holy Hyssop Serum 30 50g</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -649,15 +707,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>8809562191612</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Arencia Holy Hyssop Sheet Mask (5ea)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -670,15 +734,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>8809562191735</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Arencia Fresh Red Smoothie Serum 8 30ml</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -691,15 +761,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>8809562191889</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Arencia Fresh Red Smoothie Serum 30 50g</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -712,15 +788,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>8809562192251</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Arencia Red Collagen Jello Mask (4ea)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -733,15 +815,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>8809562191971</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Arencia Green Tea + LHA Deep Pore Rice Cake Cleanser 150g</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -754,15 +842,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>8809562192176</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Arencia Rosehip Mild PH Balancing Rice Cake Cleanser 150ml</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -775,15 +869,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>8809562192169</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Arencia Rice + LHA Pore Control Rice Cake Cleanser 150ml</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -796,15 +896,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>8809562192145</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Arencia Deep Water Surge Serum 30ml</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -817,15 +923,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>8809562192138</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>Arencia Deep Water Surge Serum 30 50g</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -838,15 +950,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>8809562192220</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Arencia Deep Water Surge Soothing Cream 110ml</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -859,15 +977,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>8809562192565</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Red Smoothie Lotion 5 200ml</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -880,15 +1004,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>8809562192572</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>Arencia Pore Melt Mochi Cleansing Oil 200ml</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -901,15 +1031,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>8809562192640</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>Honey Glazed Collagen Lip Mask 15g</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -922,15 +1058,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>8809562192763</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Arencia Retinal Booster Shot 30ml</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>540</v>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,15 +1085,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>8809562192770</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Arencia Vitamin C Booster Shot 30ml</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>540</v>
       </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -964,15 +1112,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>8809562193173</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Arencia PDRN Booster Shot 30ml</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>540</v>
       </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -985,15 +1139,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>8809562192725</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>Arencia Retinal Boosting Eye Mask 60ea 84g</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1006,15 +1166,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>8809562192664</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>Arencia PDRN + Hyaluronic Deep Hydration Pads 90ea 200ml</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1027,15 +1193,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>8809562192701</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>Pore Melt Cleansing Oil Pad</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1048,15 +1220,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>8809562192800</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>Blue Collagen Cryo Jello Mask 35gx 1EA</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,15 +1247,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>8809562192817</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>Blue Collagen Cryo Jello Mask 35gx 4EA</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1090,15 +1274,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>8809562193326</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>Arencia TXA Booster Shot 30ml</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1111,15 +1301,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>8809562193487</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Arencia NAD+ Booster Shot 30ml</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1132,15 +1328,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>8809562193302</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Arencia Eraser Shot Glycolic Acid Booster 30ml</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1153,15 +1355,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>8809562193531</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Arencia Vitamin C Booster Shot Mask (5ea)</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1174,15 +1382,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>8809562193562</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>Arencia Vita Collagen Radiance Jello Mask (4ea)</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1195,15 +1409,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>8809562193500</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>Arencia Eraser Shot Glycolic Acid Exfoliator</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1216,15 +1436,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>8809562193036</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>Arencia Vitamin C Glutathione Skin Booster Mist</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1237,15 +1463,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>8809562193265</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>Arencia Vitamin C Glutathione Booster Shot Essence</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1258,15 +1490,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>8809562193319</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>Arencia Eraser Soothing Cream</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1279,15 +1517,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>8809562193197</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Arencia Vitamin C Glow Booster Gel Cream</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1300,15 +1544,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>8809562193227</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>Arencia Vitamin C Booster Shot 10ml</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>990</v>
       </c>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1321,15 +1571,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>8809562193449</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>Arencia PDRN Booster Shot 10ml</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>990</v>
       </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1342,15 +1598,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>8809562193463</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>Arencia NAD+ Booster Shot 10ml</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>990</v>
       </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1363,15 +1625,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>8809562193456</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Arencia Eraser Shot Glycolic Acid Booster 10ml</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>990</v>
       </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1384,15 +1652,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>8809562193432</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>Arencia Retinal Booster Shot 10ml</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>990</v>
       </c>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1405,15 +1679,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>8803463009717</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 50</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1426,15 +1706,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>8809695678448</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 700</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1447,15 +1733,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>8803463003500</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 1000</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1468,15 +1760,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>8803463006020</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>VT MILD REEDLE SHOT 50 2-STEP MASK</t>
         </is>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1489,15 +1787,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>8803463009724</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 100 2-STEP MASK</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1510,15 +1814,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>8803463006044</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 300 2-STEP MASK</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1531,15 +1841,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>8803463006051</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 700 2-STEP MASK</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1552,15 +1868,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>8803463006068</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 1000 2-STEP MASK</t>
         </is>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1573,15 +1895,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>8803463008574</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 100 2-STEP MASK(5EA)</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1594,15 +1922,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>8803463000858</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT 300 2-STEP MASK(5EA)</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1615,15 +1949,25 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>8803463006037</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 100 2STEP MASK</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8803463007416 / 8803463010027</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1636,15 +1980,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>8803463010072</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 300 2STEP MASK</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1657,15 +2007,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>8803463010089</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 700 2STEP MASK</t>
         </is>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1678,15 +2034,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>8803463007607</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>VT HYDROP REEDLE SHOT 100hL 2 STEP MASK</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1699,15 +2061,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
+          <t>8803463007614</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>VT HYDROP REEDLE SHOT 300hL 2 STEP MASK</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1720,15 +2088,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>8803463007621</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>VT HYDROP REEDLE SHOT 700hL 2 STEP MASK</t>
         </is>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1741,15 +2115,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>8803463010188</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>VT HYDROP REEDLE SHOT 100hL 2 STEP MASK (5EA)</t>
         </is>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1762,15 +2142,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>8803463009847</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>VT PRO CICA REEDLE SHOT® 100 2STEP HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="E62" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1783,15 +2169,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>8803463010027</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 100 2STEP MASK</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="E63" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>8803463007416 / 8803463010027</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1804,15 +2200,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>8803463009861</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>VT VITA-LIGHT REEDLE SHOT® 100 2STEP HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="E64" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1825,15 +2227,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>8803463010577</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>VT RETI-A REEDLE SHOT® 100 2STEP HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="E65" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1846,15 +2254,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>8803463009854</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>VT HYDROP REEDLE SHOT® 100hL 2STEP HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="E66" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1867,15 +2281,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>8803463007362</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>VT PRO CICA REEDLE SHOT® 100 2STEP HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="E67" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1888,15 +2308,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>8803463007416</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 100 2STEP MASK</t>
         </is>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="E68" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8803463007416 / 8803463010027</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1909,15 +2339,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>8803463007409</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>VT VITA-LIGHT REEDLE SHOT® 100 2STEP HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="E69" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1930,15 +2366,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>8803463007386</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>VT RETI-A REEDLE SHOT® 100 2STEP HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="E70" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1951,15 +2393,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>8803463007379</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>VT HYDROP REEDLE SHOT® 100hL 2STEP HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="E71" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1972,15 +2420,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>8809695678363</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>VT 100 REEDLE SHOT</t>
         </is>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="E72" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1993,15 +2447,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>8809695678431</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>VT 300 REEDLE SHOT</t>
         </is>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="E73" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2014,15 +2474,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>8803463006396</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>VT 100 RETI-A REEDLE SHOT</t>
         </is>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="E74" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="E74" s="3" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>8803463006396 / 8803463007249</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2035,15 +2505,25 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>8803463006402</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
           <t>VT 100 VITA-LIGHT REEDLE SHOT</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="E75" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>8803463006402 / 8803463007256</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2056,15 +2536,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>8803463003692</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>VT 100 COLLAGEN REEDLE SHOT</t>
         </is>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="E76" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>8803463003692 / 8803463007317</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2077,15 +2567,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>8803463006150</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT EX COLLAGEN MODELING PACK</t>
         </is>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="E77" s="3" t="n">
         <v>540</v>
       </c>
-      <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2098,15 +2594,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>8803463006143</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT EX CICA MODELING PACK</t>
         </is>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="E78" s="3" t="n">
         <v>540</v>
       </c>
-      <c r="E78" s="3" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2119,15 +2621,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>8803463006167</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT EX VITAMIN MODELING PACK</t>
         </is>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="E79" s="3" t="n">
         <v>540</v>
       </c>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2140,15 +2648,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>8803463006174</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT EX HYALURONIC MODELING PACK</t>
         </is>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="E80" s="3" t="n">
         <v>540</v>
       </c>
-      <c r="E80" s="3" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2161,15 +2675,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>8803463007553</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>VT HYDROP REEDLE SHOT 300hL</t>
         </is>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="E81" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E81" s="3" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2182,15 +2702,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>8803463007560</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>VT HYDROP REEDLE SHOT 700hL</t>
         </is>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="E82" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E82" s="3" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2203,15 +2729,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>8803463007249</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>VT RETI-A REEDLE SHOT 100</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="E83" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>8803463006396 / 8803463007249</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2224,15 +2760,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>8803463007096</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>VT RETI-A REEDLE SHOT 300</t>
         </is>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="E84" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E84" s="3" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2245,15 +2787,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>8803463007102</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>VT RETI-A REEDLE SHOT 700</t>
         </is>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="E85" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E85" s="3" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2266,15 +2814,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>8803463007256</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>VT VITA-LIGHT REEDLE SHOT 100</t>
         </is>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="E86" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E86" s="3" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>8803463006402 / 8803463007256</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2287,15 +2845,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>8803463007119</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
           <t>VT VITA-LIGHT REEDLE SHOT 300</t>
         </is>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="E87" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E87" s="3" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2308,15 +2872,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>8803463007126</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>VT VITA-LIGHT REEDLE SHOT 700</t>
         </is>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="E88" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E88" s="3" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2329,15 +2899,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>8803463007317</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 100</t>
         </is>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="E89" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E89" s="3" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>8803463003692 / 8803463007317</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2350,15 +2930,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>8803463005733</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 300</t>
         </is>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="E90" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E90" s="3" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2371,15 +2957,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>8803463005740</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 700</t>
         </is>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="E91" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E91" s="3" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2392,15 +2984,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>8803463007324</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>VT PRO CICA REEDLE SHOT 100</t>
         </is>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="E92" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E92" s="3" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>8803463003685 / 8803463007324</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2413,15 +3015,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>8803463005719</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>VT PRO CICA REEDLE SHOT 300</t>
         </is>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="E93" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E93" s="3" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2434,15 +3042,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>8803463005726</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>VT PRO CICA REEDLE SHOT 700</t>
         </is>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="E94" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" s="3" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2455,15 +3069,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>8803463009175</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
           <t>VT RED BOOSTER REEDLE SHOT 100</t>
         </is>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="E95" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E95" s="3" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2476,15 +3096,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>8803463009663</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>VT RED BOOSTER REEDLE SHOT 300</t>
         </is>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="E96" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E96" s="3" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" s="3" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2497,15 +3123,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>8803463009670</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>VT RED BOOSTER REEDLE SHOT 700</t>
         </is>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="E97" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E97" s="3" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2518,15 +3150,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>8803463009182</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>VT SNAIL REEDLE SHOT 100B</t>
         </is>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="E98" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" s="3" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2539,15 +3177,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>8803463010867</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>VT BLACK TRUFFLE REEDLE SHOT® 100</t>
         </is>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="E99" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E99" s="3" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2560,15 +3204,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>8803463006518</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>VT REEDLE S LIP PLUMPER BEGINNER</t>
         </is>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="E100" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E100" s="3" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" s="3" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2581,15 +3231,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>8803463006501</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>VT REEDLE S LIP PLUMPER EXPERT</t>
         </is>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="E101" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E101" s="3" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" s="3" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2602,15 +3258,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>8803463012106</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>VT GARLIC AC REEDLE SHOT SPOT CREAM</t>
         </is>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="E102" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E102" s="3" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" s="3" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2623,15 +3285,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
+          <t>8803463012090</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
           <t>VT GARLIC AC REEDLE SHOT GEL CREAM</t>
         </is>
       </c>
-      <c r="D103" s="3" t="n">
+      <c r="E103" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E103" s="3" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2644,15 +3312,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>8803463012236</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT FOOT PEELING MASK</t>
         </is>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="E104" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="E104" s="3" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2665,15 +3339,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>8803463012229</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT NOURISHING HAND MASK</t>
         </is>
       </c>
-      <c r="D105" s="3" t="n">
+      <c r="E105" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" s="3" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2686,15 +3366,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>8803463007515</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>VT PDRN HYDROGEL MASK</t>
         </is>
       </c>
-      <c r="D106" s="3" t="n">
+      <c r="E106" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="E106" s="3" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" s="3" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2707,15 +3393,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
+          <t>8803463004286</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
           <t>VT PDRN ESSENCE 100</t>
         </is>
       </c>
-      <c r="D107" s="3" t="n">
+      <c r="E107" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E107" s="3" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2728,15 +3420,25 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>8803463020040</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>VT PDRN CREAM 100</t>
         </is>
       </c>
-      <c r="D108" s="3" t="n">
+      <c r="E108" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E108" s="3" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>8803463006655 / 8803463020040</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2749,15 +3451,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
+          <t>8803463006853</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT 100</t>
         </is>
       </c>
-      <c r="D109" s="3" t="n">
+      <c r="E109" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E109" s="3" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" s="3" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2770,15 +3478,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
+          <t>8803463006860</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT 300</t>
         </is>
       </c>
-      <c r="D110" s="3" t="n">
+      <c r="E110" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E110" s="3" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" s="3" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2789,17 +3503,19 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
         <is>
           <t>KR_PD_PDRN TONER_250ml_1ea</t>
         </is>
       </c>
-      <c r="D111" s="3" t="n">
+      <c r="E111" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E111" s="3" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" s="3" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2812,15 +3528,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
+          <t>8803463011659</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT HAIR AMPOULE 100dL</t>
         </is>
       </c>
-      <c r="D112" s="3" t="n">
+      <c r="E112" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E112" s="3" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" s="3" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2833,15 +3555,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
+          <t>8803463009687</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
           <t>VT PDRN GLOW AMPOULE</t>
         </is>
       </c>
-      <c r="D113" s="3" t="n">
+      <c r="E113" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="E113" s="3" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" s="3" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2854,15 +3582,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>8803463019792</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
           <t>VT PDRN CAPSULE CREAM 100</t>
         </is>
       </c>
-      <c r="D114" s="3" t="n">
+      <c r="E114" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E114" s="3" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" s="3" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2875,15 +3609,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
+          <t>8803463010744</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT SCALP SHAMPOO</t>
         </is>
       </c>
-      <c r="D115" s="3" t="n">
+      <c r="E115" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E115" s="3" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" s="3" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2896,15 +3636,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
+          <t>8803463008109</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
           <t>VT PDRN MOIST TONE UP SUN ESSENCE RX</t>
         </is>
       </c>
-      <c r="D116" s="3" t="n">
+      <c r="E116" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E116" s="3" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" s="3" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2917,15 +3663,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
+          <t>8803463012199</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT EYE LIFTER</t>
         </is>
       </c>
-      <c r="D117" s="3" t="n">
+      <c r="E117" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="E117" s="3" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" s="3" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2938,15 +3690,21 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
+          <t>8803463010379</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
           <t>VT PDRN DAILY MASK</t>
         </is>
       </c>
-      <c r="D118" s="3" t="n">
+      <c r="E118" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E118" s="3" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" s="3" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2959,15 +3717,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
+          <t>8803463010416</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
           <t>VT SKIN PACK (MILD)</t>
         </is>
       </c>
-      <c r="D119" s="3" t="n">
+      <c r="E119" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E119" s="3" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" s="3" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2980,15 +3744,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>8803463010423</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>VT SKIN PACK (SMOOTH)</t>
         </is>
       </c>
-      <c r="D120" s="3" t="n">
+      <c r="E120" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E120" s="3" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="F120" s="3" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3001,15 +3771,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>8803463010430</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
           <t>VT SKIN PACK (LUMINOUS)</t>
         </is>
       </c>
-      <c r="D121" s="3" t="n">
+      <c r="E121" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E121" s="3" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" s="3" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3020,17 +3796,19 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
         <is>
           <t>KR_OL_CRYO ICE MASK_320g_30ea</t>
         </is>
       </c>
-      <c r="D122" s="3" t="n">
+      <c r="E122" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="E122" s="3" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" s="3" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3043,15 +3821,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>8803463006587</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIFTING MASK</t>
         </is>
       </c>
-      <c r="D123" s="3" t="n">
+      <c r="E123" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E123" s="3" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+      <c r="F123" s="3" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3064,15 +3848,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
+          <t>8809695679520</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIFTING SERUM</t>
         </is>
       </c>
-      <c r="D124" s="3" t="n">
+      <c r="E124" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E124" s="3" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+      <c r="F124" s="3" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3085,15 +3875,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
+          <t>8809695679537</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIFTING CREAM</t>
         </is>
       </c>
-      <c r="D125" s="3" t="n">
+      <c r="E125" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E125" s="3" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" s="3" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3106,15 +3902,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
+          <t>8809695679544</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIFTING EYE CREAM</t>
         </is>
       </c>
-      <c r="D126" s="3" t="n">
+      <c r="E126" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E126" s="3" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" s="3" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3127,15 +3929,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>8803463008390</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>VT GLUCAMUNE MASK (1EA)</t>
         </is>
       </c>
-      <c r="D127" s="3" t="n">
+      <c r="E127" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="E127" s="3" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" s="3" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3146,17 +3954,19 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
         <is>
           <t>VT CICA RETI-A ALL IN ONE 3STEP MASK</t>
         </is>
       </c>
-      <c r="D128" s="3" t="n">
+      <c r="E128" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="E128" s="3" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" s="3" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3169,15 +3979,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>8809695677243</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
           <t>VT CICA RETI-A CREAM 0.05</t>
         </is>
       </c>
-      <c r="D129" s="3" t="n">
+      <c r="E129" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E129" s="3" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" s="3" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3190,15 +4006,21 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>8809695677236</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
           <t>VT CICA RETI-A 7 DAYS MASK</t>
         </is>
       </c>
-      <c r="D130" s="3" t="n">
+      <c r="E130" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="E130" s="3" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" s="3" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3211,15 +4033,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>8809695678028</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>VT CICA RETI-A MASK</t>
         </is>
       </c>
-      <c r="D131" s="3" t="n">
+      <c r="E131" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E131" s="3" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="F131" s="3" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3232,15 +4060,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>8803463009328</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT HYDROP CREAM SET</t>
         </is>
       </c>
-      <c r="D132" s="3" t="n">
+      <c r="E132" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E132" s="3" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" s="3" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3253,15 +4087,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
+          <t>8803463008987</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT COLLAGEN SET</t>
         </is>
       </c>
-      <c r="D133" s="3" t="n">
+      <c r="E133" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E133" s="3" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" s="3" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3272,17 +4112,19 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
         <is>
           <t>VT PRO CICA CENTELLA ASIATICA TIGER CLEAR SPOT PATCH 4pcs/15ea*2+18ea*2(66EA)</t>
         </is>
       </c>
-      <c r="D134" s="3" t="n">
+      <c r="E134" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E134" s="3" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" s="3" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3293,17 +4135,19 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
         <is>
           <t>VT SPOT PATCH(3sets, 48ea)</t>
         </is>
       </c>
-      <c r="D135" s="3" t="n">
+      <c r="E135" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E135" s="3" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" s="3" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3316,15 +4160,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
+          <t>8809559627506</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
           <t>VT CICA MILD CLEANSING TISSUE</t>
         </is>
       </c>
-      <c r="D136" s="3" t="n">
+      <c r="E136" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E136" s="3" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" s="3" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3337,15 +4187,21 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>8803463007461</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>VT CICA CREAM PLUS (100ml)</t>
         </is>
       </c>
-      <c r="D137" s="3" t="n">
+      <c r="E137" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="E137" s="3" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" s="3" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3358,15 +4214,21 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>8803463007508</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>VT CICA CREAM PLUS (30ml)</t>
         </is>
       </c>
-      <c r="D138" s="3" t="n">
+      <c r="E138" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E138" s="3" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" s="3" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3379,15 +4241,21 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>8803463003593</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
           <t>VT CICA-EXOSOME MOISTURE MASK</t>
         </is>
       </c>
-      <c r="D139" s="3" t="n">
+      <c r="E139" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E139" s="3" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" s="3" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3400,15 +4268,21 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>8809559627490</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
           <t>VT CICA DAILY SOOTHING MASK</t>
         </is>
       </c>
-      <c r="D140" s="3" t="n">
+      <c r="E140" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E140" s="3" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" s="3" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3421,15 +4295,21 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
+          <t>8803463012601</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
           <t>VT CICA MASK CLEANSER</t>
         </is>
       </c>
-      <c r="D141" s="3" t="n">
+      <c r="E141" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E141" s="3" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" s="3" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3440,17 +4320,19 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
         <is>
           <t>VT CICA COLLAGEN ALL IN ONE 3STEP MASK</t>
         </is>
       </c>
-      <c r="D142" s="3" t="n">
+      <c r="E142" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="E142" s="3" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" s="3" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3463,15 +4345,21 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
+          <t>8809695677281</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
           <t>VT CICA COLLAGEN MASK</t>
         </is>
       </c>
-      <c r="D143" s="3" t="n">
+      <c r="E143" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E143" s="3" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" s="3" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3484,15 +4372,21 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
+          <t>8809695677199</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
           <t>VT CICA COLLAGEN CREAM</t>
         </is>
       </c>
-      <c r="D144" s="3" t="n">
+      <c r="E144" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E144" s="3" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" s="3" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3505,15 +4399,21 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
+          <t>8803463003517</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
           <t>VT CICA COLLAGEN EYE CREAM</t>
         </is>
       </c>
-      <c r="D145" s="3" t="n">
+      <c r="E145" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E145" s="3" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" s="3" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3524,17 +4424,19 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
         <is>
           <t>VT VITA-LIGHT ALL IN ONE 3STEP MASK</t>
         </is>
       </c>
-      <c r="D146" s="3" t="n">
+      <c r="E146" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="E146" s="3" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" s="3" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3547,15 +4449,21 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
+          <t>8803463006242</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT VITA-LIGHT BRIGHTENING MASK</t>
         </is>
       </c>
-      <c r="D147" s="3" t="n">
+      <c r="E147" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E147" s="3" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" s="3" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3568,15 +4476,21 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
+          <t>8803463008567</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIP PLUMPER CRYSTAL</t>
         </is>
       </c>
-      <c r="D148" s="3" t="n">
+      <c r="E148" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E148" s="3" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+      <c r="F148" s="3" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3589,15 +4503,21 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
+          <t>8803463008598</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIP PLUMPER TWINKLE</t>
         </is>
       </c>
-      <c r="D149" s="3" t="n">
+      <c r="E149" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E149" s="3" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" s="3" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3610,15 +4530,21 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
+          <t>8803463009366</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIP PLUMPER USAGI PINK</t>
         </is>
       </c>
-      <c r="D150" s="3" t="n">
+      <c r="E150" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E150" s="3" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" s="3" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3631,15 +4557,21 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
+          <t>8803463009373</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT LIP PLUMPER ROSE BERRY</t>
         </is>
       </c>
-      <c r="D151" s="3" t="n">
+      <c r="E151" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="E151" s="3" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" s="3" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3652,15 +4584,21 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
+          <t>8803463012618</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
           <t>VT GLOW LOCK MASK</t>
         </is>
       </c>
-      <c r="D152" s="3" t="n">
+      <c r="E152" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E152" s="3" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" s="3" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3673,15 +4611,21 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
+          <t>8803463012625</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
           <t>VT AZ CARE LOCK MASK</t>
         </is>
       </c>
-      <c r="D153" s="3" t="n">
+      <c r="E153" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E153" s="3" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" s="3" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3694,15 +4638,21 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>8803463014407</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
           <t>VT PDRN TENSION TONER PAD</t>
         </is>
       </c>
-      <c r="D154" s="3" t="n">
+      <c r="E154" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E154" s="3" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" s="3" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3715,15 +4665,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
+          <t>8803463007065</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT CREAM</t>
         </is>
       </c>
-      <c r="D155" s="3" t="n">
+      <c r="E155" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E155" s="3" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" s="3" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3736,15 +4692,21 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
+          <t>8803463014070</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
           <t>VT GLYCOLIC REEDLE SHOT HEAD TO TOE MIST</t>
         </is>
       </c>
-      <c r="D156" s="3" t="n">
+      <c r="E156" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E156" s="3" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+      <c r="F156" s="3" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3757,15 +4719,21 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
+          <t>8803463015435</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
           <t>VT CERAMIDE AQUA CLEANSING OIL</t>
         </is>
       </c>
-      <c r="D157" s="3" t="n">
+      <c r="E157" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="E157" s="3" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
+      <c r="F157" s="3" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3778,15 +4746,21 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
+          <t>8803463009762</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT HAIR AMPOULE 100dL</t>
         </is>
       </c>
-      <c r="D158" s="3" t="n">
+      <c r="E158" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E158" s="3" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
+      <c r="F158" s="3" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3799,15 +4773,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
+          <t>8803463009779</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT HAIR AMPOULE 300dL</t>
         </is>
       </c>
-      <c r="D159" s="3" t="n">
+      <c r="E159" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E159" s="3" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
+      <c r="F159" s="3" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3820,15 +4800,21 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
+          <t>8803463009960</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT HAIR AMPOULE 700dL</t>
         </is>
       </c>
-      <c r="D160" s="3" t="n">
+      <c r="E160" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E160" s="3" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" s="3" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3841,15 +4827,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
+          <t>8803463011420</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT SHAMPOO, TREATMENT DUO SET</t>
         </is>
       </c>
-      <c r="D161" s="3" t="n">
+      <c r="E161" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E161" s="3" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
+      <c r="F161" s="3" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3862,15 +4854,21 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
+          <t>8803463013202</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
           <t>PDRN REEDLE SHOT GOLD ESSENCE</t>
         </is>
       </c>
-      <c r="D162" s="3" t="n">
+      <c r="E162" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E162" s="3" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
+      <c r="F162" s="3" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3883,15 +4881,21 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
+          <t>8803463013219</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
           <t>PDRN REEDLE SHOT GOLD CREAM</t>
         </is>
       </c>
-      <c r="D163" s="3" t="n">
+      <c r="E163" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E163" s="3" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
+      <c r="F163" s="3" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3904,15 +4908,21 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
+          <t>8803463016753</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
           <t>VT COLLAGEN REEDLE SHOT 100(30ml)</t>
         </is>
       </c>
-      <c r="D164" s="3" t="n">
+      <c r="E164" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E164" s="3" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
+      <c r="F164" s="3" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3925,15 +4935,21 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
+          <t>8803463016746</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
           <t>VT VITA-LIGHT REEDLE SHOT 100(30ml)</t>
         </is>
       </c>
-      <c r="D165" s="3" t="n">
+      <c r="E165" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E165" s="3" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" s="3" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3946,15 +4962,21 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
+          <t>8803463016739</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
           <t>VT RED BOOSTER REEDLE SHOT 100(30ml)</t>
         </is>
       </c>
-      <c r="D166" s="3" t="n">
+      <c r="E166" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E166" s="3" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="F166" s="3" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3967,15 +4989,21 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
+          <t>8803463017491</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
           <t>VT PDRN REEDLE SHOT BRUSH HAIR SERUM</t>
         </is>
       </c>
-      <c r="D167" s="3" t="n">
+      <c r="E167" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E167" s="3" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+      <c r="F167" s="3" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3988,15 +5016,21 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
+          <t>8803463016883</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
           <t>VT CAFFENE EYE PATCH</t>
         </is>
       </c>
-      <c r="D168" s="3" t="n">
+      <c r="E168" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E168" s="3" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" s="3" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4009,15 +5043,21 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
+          <t>8803463012717</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
           <t>VT REEDLE SHOT FOR MEN ALL IN ONE</t>
         </is>
       </c>
-      <c r="D169" s="3" t="n">
+      <c r="E169" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E169" s="3" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" s="3" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4030,15 +5070,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
+          <t>8803463013325</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
           <t>VT BAKUCHIOL REEDLE SHOT CREAM</t>
         </is>
       </c>
-      <c r="D170" s="3" t="n">
+      <c r="E170" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E170" s="3" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" s="3" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4051,15 +5097,21 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
+          <t>8803463017880</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
           <t>VT RETINAL PEPTIDE CAPSULE CREAM</t>
         </is>
       </c>
-      <c r="D171" s="3" t="n">
+      <c r="E171" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E171" s="3" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" s="3" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4072,15 +5124,21 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
+          <t>8803463018726</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
           <t>VT PDRN BARRIER CLEANSER</t>
         </is>
       </c>
-      <c r="D172" s="3" t="n">
+      <c r="E172" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E172" s="3" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" s="3" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4093,15 +5151,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
+          <t>8803463017934</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
           <t>VT PDRN HYDROGEL EYE PATCH</t>
         </is>
       </c>
-      <c r="D173" s="3" t="n">
+      <c r="E173" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E173" s="3" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" s="3" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4114,15 +5178,21 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
+          <t>8803463017712</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
           <t>VT RICE CAPSULE CREAM</t>
         </is>
       </c>
-      <c r="D174" s="3" t="n">
+      <c r="E174" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E174" s="3" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" s="3" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4135,15 +5205,21 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
+          <t>8803463018108</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
           <t>VT AZELAIC ACID CARE CAPSULE CREAM</t>
         </is>
       </c>
-      <c r="D175" s="3" t="n">
+      <c r="E175" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E175" s="3" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" s="3" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -4156,15 +5232,21 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
+          <t>8803463017859</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
           <t>VT VITAMIN C ASTAXANTHIN CAPSULE CREAM</t>
         </is>
       </c>
-      <c r="D176" s="3" t="n">
+      <c r="E176" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E176" s="3" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" s="3" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -4177,15 +5259,21 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
+          <t>8803463017927</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
           <t>VT VITAMIN C ASTAXANTHIN MASK</t>
         </is>
       </c>
-      <c r="D177" s="3" t="n">
+      <c r="E177" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E177" s="3" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" s="3" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -4198,15 +5286,21 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
+          <t>8809508850597</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
           <t>PETITFEE GOLD Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D178" s="3" t="n">
+      <c r="E178" s="3" t="n">
         <v>432</v>
       </c>
-      <c r="E178" s="3" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" s="3" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4219,15 +5313,21 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
+          <t>8809508850603</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
           <t>PETITFEE BLACK PEARL &amp; GOLD Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D179" s="3" t="n">
+      <c r="E179" s="3" t="n">
         <v>576</v>
       </c>
-      <c r="E179" s="3" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" s="3" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4240,15 +5340,21 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
+          <t>8809239802872</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
           <t>PETITFEE GOLD &amp; SNAIL Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D180" s="3" t="n">
+      <c r="E180" s="3" t="n">
         <v>432</v>
       </c>
-      <c r="E180" s="3" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+      <c r="F180" s="3" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4261,15 +5367,21 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
+          <t>8809239800458</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
           <t>PETITFEE Collagen &amp; CoQ10 Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D181" s="3" t="n">
+      <c r="E181" s="3" t="n">
         <v>576</v>
       </c>
-      <c r="E181" s="3" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" s="3" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4282,15 +5394,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
+          <t>8809239800618</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
           <t>PETITFEE GOLD &amp; EGF Hydrogel Eye•Spot Patch</t>
         </is>
       </c>
-      <c r="D182" s="3" t="n">
+      <c r="E182" s="3" t="n">
         <v>432</v>
       </c>
-      <c r="E182" s="3" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+      <c r="F182" s="3" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4303,15 +5421,21 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
+          <t>8809508850429</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
           <t>PETITFEE Agave Cooling Hydrogel Eye Mask</t>
         </is>
       </c>
-      <c r="D183" s="3" t="n">
+      <c r="E183" s="3" t="n">
         <v>720</v>
       </c>
-      <c r="E183" s="3" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" s="3" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4324,15 +5448,21 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
+          <t>8809508850412</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
           <t>PETITFEE Chamomile Lightening Hydrogel Eye Mask</t>
         </is>
       </c>
-      <c r="D184" s="3" t="n">
+      <c r="E184" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="E184" s="3" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+      <c r="F184" s="3" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4345,15 +5475,21 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
+          <t>8809508850559</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
           <t>PETITFEE Artichoke Soothing Hydrogel Eye Mask</t>
         </is>
       </c>
-      <c r="D185" s="3" t="n">
+      <c r="E185" s="3" t="n">
         <v>576</v>
       </c>
-      <c r="E185" s="3" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" s="3" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4366,15 +5502,21 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
+          <t>8809508850696</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
           <t>PETITFEE Cacao Energizing Hydrogel Eye Mask</t>
         </is>
       </c>
-      <c r="D186" s="3" t="n">
+      <c r="E186" s="3" t="n">
         <v>576</v>
       </c>
-      <c r="E186" s="3" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" s="3" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4387,15 +5529,21 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
+          <t>8809508850450</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
           <t>PETITFEE Agave Cooling Hydrogel Face Mask</t>
         </is>
       </c>
-      <c r="D187" s="3" t="n">
+      <c r="E187" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E187" s="3" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+      <c r="F187" s="3" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4408,15 +5556,21 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
+          <t>8809508850467</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
           <t>PETITFEE Chamomile Lightening Hydrogel Face Mask</t>
         </is>
       </c>
-      <c r="D188" s="3" t="n">
+      <c r="E188" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E188" s="3" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
+      <c r="F188" s="3" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4429,15 +5583,21 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
+          <t>8809508850566</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
           <t>PETITFEE Artichoke Soothing Hydrogel Face Mask</t>
         </is>
       </c>
-      <c r="D189" s="3" t="n">
+      <c r="E189" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E189" s="3" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" s="3" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4450,15 +5610,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
+          <t>8809508850689</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
           <t>PETITFEE Cacao Energizing Hydrogel Face Mask</t>
         </is>
       </c>
-      <c r="D190" s="3" t="n">
+      <c r="E190" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E190" s="3" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" s="3" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4471,15 +5637,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
+          <t>8809508851822</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
           <t>Petitfee Beautifying Pore Pads</t>
         </is>
       </c>
-      <c r="D191" s="3" t="n">
+      <c r="E191" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E191" s="3" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+      <c r="F191" s="3" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4492,15 +5664,21 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
+          <t>8809508850801</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
           <t>PETITFEE Aura Quartz HYDROGEL EYE MASK PURE OPAL</t>
         </is>
       </c>
-      <c r="D192" s="3" t="n">
+      <c r="E192" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E192" s="3" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
+      <c r="F192" s="3" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4513,15 +5691,21 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>8809508851662</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
           <t>Petitfee Aura Quartz Hydrogel Eye Mask (Blue)</t>
         </is>
       </c>
-      <c r="D193" s="3" t="n">
+      <c r="E193" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="E193" s="3" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" s="3" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4534,15 +5718,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
+          <t>8809508851655</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
           <t>Petitfee Aura Quartz Lip Mask</t>
         </is>
       </c>
-      <c r="D194" s="3" t="n">
+      <c r="E194" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E194" s="3" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
+      <c r="F194" s="3" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4555,15 +5745,21 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
+          <t>8809508851228</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
           <t>Petitfee Aura Quartz Hydrogel Face Mask Crystal Rose</t>
         </is>
       </c>
-      <c r="D195" s="3" t="n">
+      <c r="E195" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E195" s="3" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
+      <c r="F195" s="3" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4576,15 +5772,21 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
+          <t>8809239800434</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
           <t>PETITFEE Dry Essence Hand Pack</t>
         </is>
       </c>
-      <c r="D196" s="3" t="n">
+      <c r="E196" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E196" s="3" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
+      <c r="F196" s="3" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4597,15 +5799,21 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
+          <t>8809239800441</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
           <t>PETITFEE Dry Essence Foot Pack</t>
         </is>
       </c>
-      <c r="D197" s="3" t="n">
+      <c r="E197" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E197" s="3" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" s="3" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4618,15 +5826,21 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
+          <t>8809239803008</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
           <t>PETITFEE GOLD Neck Pack</t>
         </is>
       </c>
-      <c r="D198" s="3" t="n">
+      <c r="E198" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="E198" s="3" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
+      <c r="F198" s="3" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -4639,15 +5853,21 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
+          <t>8809508850795</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
           <t>PETITFEE Centella Clearing Spot Patch</t>
         </is>
       </c>
-      <c r="D199" s="3" t="n">
+      <c r="E199" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E199" s="3" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
+      <c r="F199" s="3" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -4660,15 +5880,21 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
+          <t>8809508850856</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
           <t>PETITFEE Blackhead Melting Mask</t>
         </is>
       </c>
-      <c r="D200" s="3" t="n">
+      <c r="E200" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="E200" s="3" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" s="3" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4681,15 +5907,21 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
+          <t>8809508850948</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
           <t>PETITFEE Blackhead Removing Strips</t>
         </is>
       </c>
-      <c r="D201" s="3" t="n">
+      <c r="E201" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E201" s="3" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
+      <c r="F201" s="3" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -4702,15 +5934,21 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
+          <t>8809508850504</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
           <t>PETITFEE β-Glucan Deep Firming Eye Mask</t>
         </is>
       </c>
-      <c r="D202" s="3" t="n">
+      <c r="E202" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E202" s="3" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
+      <c r="F202" s="3" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -4723,15 +5961,21 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
+          <t>8809508850498</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
           <t>PETITFEE Pink Vita Brightening Eye Mask</t>
         </is>
       </c>
-      <c r="D203" s="3" t="n">
+      <c r="E203" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E203" s="3" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
+      <c r="F203" s="3" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -4744,15 +5988,21 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
+          <t>8809508850405</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
           <t>PETITFEE Pep-Tightening Eye Cream</t>
         </is>
       </c>
-      <c r="D204" s="3" t="n">
+      <c r="E204" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E204" s="3" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
+      <c r="F204" s="3" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -4765,15 +6015,21 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
+          <t>8809508851259</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
           <t>PETITFEE 10Day Centella Eye Mask Soothing</t>
         </is>
       </c>
-      <c r="D205" s="3" t="n">
+      <c r="E205" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="E205" s="3" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
+      <c r="F205" s="3" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -4786,15 +6042,21 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
+          <t>8809508851235</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
           <t>PETITFEE 10Day Peptide Eye Mask Rejuvenating</t>
         </is>
       </c>
-      <c r="D206" s="3" t="n">
+      <c r="E206" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="E206" s="3" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" s="3" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -4807,15 +6069,21 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>8809508851242</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
           <t>PETITFEE 10Day Vitamin Eye Mask Brightening</t>
         </is>
       </c>
-      <c r="D207" s="3" t="n">
+      <c r="E207" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="E207" s="3" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
+      <c r="F207" s="3" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -4828,15 +6096,21 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
+          <t>8809239801820</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
           <t>PETITFEE BLACK PEARL &amp; GOLD Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D208" s="3" t="n">
+      <c r="E208" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="E208" s="3" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
+      <c r="F208" s="3" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -4849,15 +6123,21 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
+          <t>8809239803596</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
           <t>PETITFEE GOLD Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D209" s="3" t="n">
+      <c r="E209" s="3" t="n">
         <v>880</v>
       </c>
-      <c r="E209" s="3" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
+      <c r="F209" s="3" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -4868,17 +6148,19 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
         <is>
           <t>Koelf Lemon &amp; Basil Ice Pop Hydrogel Eye Mask</t>
         </is>
       </c>
-      <c r="D210" s="3" t="n">
+      <c r="E210" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E210" s="3" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
+      <c r="F210" s="3" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -4889,17 +6171,19 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
         <is>
           <t>Koelf Blueberry &amp; Cream Ice Pop Hydrogel Eye Mask</t>
         </is>
       </c>
-      <c r="D211" s="3" t="n">
+      <c r="E211" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E211" s="3" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
+      <c r="F211" s="3" t="inlineStr"/>
       <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -4910,17 +6194,19 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
         <is>
           <t>Koelf Ruby &amp; Bulgarian Rose Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D212" s="3" t="n">
+      <c r="E212" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E212" s="3" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
+      <c r="F212" s="3" t="inlineStr"/>
       <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -4931,17 +6217,19 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
         <is>
           <t>Koelf Gold &amp; Royal Jelly Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D213" s="3" t="n">
+      <c r="E213" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E213" s="3" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
+      <c r="F213" s="3" t="inlineStr"/>
       <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -4952,17 +6240,19 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
         <is>
           <t>Koelf Pearl &amp; Shea Butter Hydrogel Eye Patch</t>
         </is>
       </c>
-      <c r="D214" s="3" t="n">
+      <c r="E214" s="3" t="n">
         <v>216</v>
       </c>
-      <c r="E214" s="3" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
+      <c r="F214" s="3" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -4973,17 +6263,19 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
         <is>
           <t>Koelf Melting Essence Hand Pack (10 uses)</t>
         </is>
       </c>
-      <c r="D215" s="3" t="n">
+      <c r="E215" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E215" s="3" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
+      <c r="F215" s="3" t="inlineStr"/>
       <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -4994,17 +6286,19 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
         <is>
           <t>Koelf Melting Essence Foot Pack (10 uses)</t>
         </is>
       </c>
-      <c r="D216" s="3" t="n">
+      <c r="E216" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E216" s="3" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
+      <c r="F216" s="3" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -5017,15 +6311,21 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
+          <t>8809733216137</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
           <t>LAMELIN ANTI AGING ROLL ON EYE CREAM _ RETINOL</t>
         </is>
       </c>
-      <c r="D217" s="3" t="n">
+      <c r="E217" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E217" s="3" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
+      <c r="F217" s="3" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -5038,15 +6338,21 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
+          <t>8809733216144</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
           <t>LAMELIN ANTI AGING ROLL ON EYE CREAM _ COLLAGEN</t>
         </is>
       </c>
-      <c r="D218" s="3" t="n">
+      <c r="E218" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E218" s="3" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
+      <c r="F218" s="3" t="inlineStr"/>
       <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -5059,15 +6365,21 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
+          <t>8809733216151</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
           <t>LAMELIN ANTI AGING ROLL ON EYE CREAM _ PLACENTA</t>
         </is>
       </c>
-      <c r="D219" s="3" t="n">
+      <c r="E219" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E219" s="3" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
+      <c r="F219" s="3" t="inlineStr"/>
       <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -5080,15 +6392,21 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
+          <t>8809733217066</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
           <t>LAMELIN HYALURONIC CALMING TONER</t>
         </is>
       </c>
-      <c r="D220" s="3" t="n">
+      <c r="E220" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E220" s="3" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
+      <c r="F220" s="3" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -5101,15 +6419,21 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
+          <t>8809733217073</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
           <t>LAMELIN CICA CALMING TONER</t>
         </is>
       </c>
-      <c r="D221" s="3" t="n">
+      <c r="E221" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E221" s="3" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
+      <c r="F221" s="3" t="inlineStr"/>
       <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -5122,15 +6446,21 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
+          <t>8809733217080</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
           <t>LAMELIN COLLAGEN CALMING TONER</t>
         </is>
       </c>
-      <c r="D222" s="3" t="n">
+      <c r="E222" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E222" s="3" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
+      <c r="F222" s="3" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -5143,15 +6473,21 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
+          <t>8809733213693</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
           <t>LAMELIN HYALURONIC 4 IN 1 CREAM</t>
         </is>
       </c>
-      <c r="D223" s="3" t="n">
+      <c r="E223" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E223" s="3" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
+      <c r="F223" s="3" t="inlineStr"/>
       <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -5164,15 +6500,25 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
+          <t>8809733213655</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
           <t>LAMELIN COLLAGEN 4 IN 1 CREAM</t>
         </is>
       </c>
-      <c r="D224" s="3" t="n">
+      <c r="E224" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E224" s="3" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
+      <c r="F224" s="3" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>8809733213655 / 8809733213679</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -5185,15 +6531,21 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
+          <t>8809733213662</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
           <t>LAMELIN VITAMIN 4 IN 1 CREAM</t>
         </is>
       </c>
-      <c r="D225" s="3" t="n">
+      <c r="E225" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E225" s="3" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
+      <c r="F225" s="3" t="inlineStr"/>
       <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -5206,15 +6558,25 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
+          <t>8809733213679</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
           <t>LAMELIN COLLAGEN 4 IN 1 CREAM</t>
         </is>
       </c>
-      <c r="D226" s="3" t="n">
+      <c r="E226" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E226" s="3" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
+      <c r="F226" s="3" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>8809733213655 / 8809733213679</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -5227,15 +6589,21 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
+          <t>8809733213686</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
           <t>LAMELIN CICA 4 IN 1 CREAM</t>
         </is>
       </c>
-      <c r="D227" s="3" t="n">
+      <c r="E227" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E227" s="3" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
+      <c r="F227" s="3" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -5248,15 +6616,21 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
+          <t>8809733216502</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
           <t>LAMELIN MILD CLEANSING FOAM HYALURONIC</t>
         </is>
       </c>
-      <c r="D228" s="3" t="n">
+      <c r="E228" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E228" s="3" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
+      <c r="F228" s="3" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -5269,15 +6643,21 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
+          <t>8809733216496</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
           <t>LAMELIN MILD CLEANSING FOAM COLLAGEN</t>
         </is>
       </c>
-      <c r="D229" s="3" t="n">
+      <c r="E229" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E229" s="3" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
+      <c r="F229" s="3" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -5290,15 +6670,21 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
+          <t>8809733216489</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
           <t>LAMELIN MILD CLEANSING FOAM CICA</t>
         </is>
       </c>
-      <c r="D230" s="3" t="n">
+      <c r="E230" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E230" s="3" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="F230" s="3" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5311,15 +6697,21 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
+          <t>8809733216519</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
           <t>LAMELIN MILD CLEANSING SCRUB FOAM RICE</t>
         </is>
       </c>
-      <c r="D231" s="3" t="n">
+      <c r="E231" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E231" s="3" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+      <c r="F231" s="3" t="inlineStr"/>
       <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -5332,15 +6724,21 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
+          <t>8809733216540</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
           <t>LAMELIN MILD PEELING GEL HYALURONIC</t>
         </is>
       </c>
-      <c r="D232" s="3" t="n">
+      <c r="E232" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E232" s="3" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
+      <c r="F232" s="3" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -5353,15 +6751,21 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
+          <t>8809733216533</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
           <t>LAMELIN MILD PEELING GEL COLLAGEN</t>
         </is>
       </c>
-      <c r="D233" s="3" t="n">
+      <c r="E233" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E233" s="3" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" s="3" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -5374,15 +6778,21 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
+          <t>8809733216526</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
           <t>LAMELIN MILD PEELING GEL CICA</t>
         </is>
       </c>
-      <c r="D234" s="3" t="n">
+      <c r="E234" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E234" s="3" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+      <c r="F234" s="3" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -5395,15 +6805,21 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
+          <t>8800248332008</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
           <t>LAMELIN ANIMAL MASK SHEET TIGER</t>
         </is>
       </c>
-      <c r="D235" s="3" t="n">
+      <c r="E235" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E235" s="3" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+      <c r="F235" s="3" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -5416,15 +6832,21 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
+          <t>8800248331971</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
           <t>LAMELIN ANIMAL MASK SHEET PUPPY</t>
         </is>
       </c>
-      <c r="D236" s="3" t="n">
+      <c r="E236" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E236" s="3" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" s="3" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -5437,15 +6859,21 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
+          <t>8800248331995</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
           <t>LAMELIN ANIMAL MASK SHEET PANDA</t>
         </is>
       </c>
-      <c r="D237" s="3" t="n">
+      <c r="E237" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E237" s="3" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
+      <c r="F237" s="3" t="inlineStr"/>
       <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -5458,15 +6886,21 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
+          <t>8800248331988</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
           <t>LAMELIN ANIMAL MASK SHEET CAT</t>
         </is>
       </c>
-      <c r="D238" s="3" t="n">
+      <c r="E238" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E238" s="3" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" s="3" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -5479,15 +6913,21 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
+          <t>8809733219046</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
           <t>LAMELIN SELF CARE MODELING PACK - CICA</t>
         </is>
       </c>
-      <c r="D239" s="3" t="n">
+      <c r="E239" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E239" s="3" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
+      <c r="F239" s="3" t="inlineStr"/>
       <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -5500,15 +6940,21 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
+          <t>8809733219053</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
           <t>LAMELIN SELF CARE MODELING PACK - COLLGEN</t>
         </is>
       </c>
-      <c r="D240" s="3" t="n">
+      <c r="E240" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E240" s="3" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
+      <c r="F240" s="3" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -5521,15 +6967,21 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
+          <t>8809733219060</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
           <t>LAMELIN SELF CARE MODELING PACK - VITAMIN</t>
         </is>
       </c>
-      <c r="D241" s="3" t="n">
+      <c r="E241" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E241" s="3" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
+      <c r="F241" s="3" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -5542,15 +6994,21 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
+          <t>8809733215956</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
           <t>LAMELIN SPA FOOT PEELING</t>
         </is>
       </c>
-      <c r="D242" s="3" t="n">
+      <c r="E242" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E242" s="3" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
+      <c r="F242" s="3" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -5563,15 +7021,21 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
+          <t>8800248331766</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
           <t>LAMELIN DEEP MOISTURE HAND MASK</t>
         </is>
       </c>
-      <c r="D243" s="3" t="n">
+      <c r="E243" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E243" s="3" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
+      <c r="F243" s="3" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -5584,15 +7048,21 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
+          <t>8800248331773</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
           <t>LAMELIN DEEP MOISTURE FOOT MASK</t>
         </is>
       </c>
-      <c r="D244" s="3" t="n">
+      <c r="E244" s="3" t="n">
         <v>640</v>
       </c>
-      <c r="E244" s="3" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" s="3" t="inlineStr"/>
       <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -5605,15 +7075,21 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
+          <t>8809733217226</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
           <t>LAMELIN PERFECT SEBUM CUT POWDER</t>
         </is>
       </c>
-      <c r="D245" s="3" t="n">
+      <c r="E245" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="E245" s="3" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" s="3" t="inlineStr"/>
       <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -5626,15 +7102,25 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
+          <t>8809941826302</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
           <t>MEDIPEEL RETINAL NMN BOUNCE SHOT BOOSTER</t>
         </is>
       </c>
-      <c r="D246" s="3" t="n">
+      <c r="E246" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E246" s="3" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" s="3" t="inlineStr"/>
       <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>8809941826302 / 8809941826555</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -5647,15 +7133,25 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
+          <t>8809941826586</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
           <t>MEDIPEEL RETINAL NMN BOUNCE SHOT EYE CREAM REFILL</t>
         </is>
       </c>
-      <c r="D247" s="3" t="n">
+      <c r="E247" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="E247" s="3" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
+      <c r="F247" s="3" t="inlineStr"/>
       <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>8809941826579 / 8809941826586</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -5668,15 +7164,25 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
+          <t>8809941826319</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
           <t>MEDIPEEL RETINAL NMN BOUNCE SHOT EYE CREAM</t>
         </is>
       </c>
-      <c r="D248" s="3" t="n">
+      <c r="E248" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="E248" s="3" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" s="3" t="inlineStr"/>
       <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>8809941826319 / 8809941826562</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -5689,15 +7195,21 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
+          <t>8809941825152</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN 3,000 SHOT SERUM</t>
         </is>
       </c>
-      <c r="D249" s="3" t="n">
+      <c r="E249" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E249" s="3" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
+      <c r="F249" s="3" t="inlineStr"/>
       <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -5710,15 +7222,25 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
+          <t>8809941827316</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN LIFTING SHOT DROP GEL CREAM</t>
         </is>
       </c>
-      <c r="D250" s="3" t="n">
+      <c r="E250" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E250" s="3" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
+      <c r="F250" s="3" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>8809941825794 / 8809941827316</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -5731,15 +7253,21 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
+          <t>8809941826371</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN LIFTING SHOT MIST</t>
         </is>
       </c>
-      <c r="D251" s="3" t="n">
+      <c r="E251" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E251" s="3" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
+      <c r="F251" s="3" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -5752,15 +7280,21 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
+          <t>8809941826333</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN LIFTING SHOT SERUM</t>
         </is>
       </c>
-      <c r="D252" s="3" t="n">
+      <c r="E252" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E252" s="3" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
+      <c r="F252" s="3" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -5773,15 +7307,21 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
+          <t>8809941826364</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN LIFTING SHOT EYE CREAM</t>
         </is>
       </c>
-      <c r="D253" s="3" t="n">
+      <c r="E253" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E253" s="3" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
+      <c r="F253" s="3" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -5794,15 +7334,21 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
+          <t>8809941826340</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN LIFTING SHOT AMPOULE</t>
         </is>
       </c>
-      <c r="D254" s="3" t="n">
+      <c r="E254" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E254" s="3" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
+      <c r="F254" s="3" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -5815,15 +7361,21 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
+          <t>8809941826357</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN LIFTING SHOT CREAM</t>
         </is>
       </c>
-      <c r="D255" s="3" t="n">
+      <c r="E255" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E255" s="3" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" s="3" t="inlineStr"/>
       <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -5836,15 +7388,21 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
+          <t>8809941826326</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN LIFTING SHOT TONER</t>
         </is>
       </c>
-      <c r="D256" s="3" t="n">
+      <c r="E256" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E256" s="3" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
+      <c r="F256" s="3" t="inlineStr"/>
       <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -5857,15 +7415,21 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
+          <t>8809941826173</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN MICRO SHOT POWDER CLEANSER</t>
         </is>
       </c>
-      <c r="D257" s="3" t="n">
+      <c r="E257" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E257" s="3" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
+      <c r="F257" s="3" t="inlineStr"/>
       <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -5878,15 +7442,21 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
+          <t>8809941826548</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO EX PDRN MELTING GLOW LIP SLEEPING MASK</t>
         </is>
       </c>
-      <c r="D258" s="3" t="n">
+      <c r="E258" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E258" s="3" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
+      <c r="F258" s="3" t="inlineStr"/>
       <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -5899,15 +7469,21 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
+          <t>8809941824186</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VOLUME BIO TOX GRINDING CLEANSING BALM PRO</t>
         </is>
       </c>
-      <c r="D259" s="3" t="n">
+      <c r="E259" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E259" s="3" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
+      <c r="F259" s="3" t="inlineStr"/>
       <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -5920,15 +7496,21 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
+          <t>8809941825244</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
           <t>MEDIPEEL COLLAGEN GLOW WRAPPING MASK</t>
         </is>
       </c>
-      <c r="D260" s="3" t="n">
+      <c r="E260" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E260" s="3" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
+      <c r="F260" s="3" t="inlineStr"/>
       <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -5941,15 +7523,21 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
+          <t>8809941824339</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VOLUME BIO TOX GRINDING LIP AND FACE AMPOULE BALM PRO</t>
         </is>
       </c>
-      <c r="D261" s="3" t="n">
+      <c r="E261" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="E261" s="3" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
+      <c r="F261" s="3" t="inlineStr"/>
       <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -5962,15 +7550,21 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
+          <t>8809941820621</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTID 9 VOLUME BIO TOX AMPOULE PRO</t>
         </is>
       </c>
-      <c r="D262" s="3" t="n">
+      <c r="E262" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E262" s="3" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
+      <c r="F262" s="3" t="inlineStr"/>
       <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -5983,15 +7577,21 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
+          <t>8809941820317</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTID 9 VOLUME BIO TOX TONER PRO</t>
         </is>
       </c>
-      <c r="D263" s="3" t="n">
+      <c r="E263" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E263" s="3" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
+      <c r="F263" s="3" t="inlineStr"/>
       <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -6004,15 +7604,25 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
+          <t>8809941820430</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VOLUME AND TENSION TOX CREAM PRO</t>
         </is>
       </c>
-      <c r="D264" s="3" t="n">
+      <c r="E264" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E264" s="3" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
+      <c r="F264" s="3" t="inlineStr"/>
       <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>8809941820430 / 8809941826722</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -6025,15 +7635,21 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
+          <t>8809409340548</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
           <t>MEDI-PEEL 24K GOLD SNAIL REPAIR EYE CREAM</t>
         </is>
       </c>
-      <c r="D265" s="3" t="n">
+      <c r="E265" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E265" s="3" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
+      <c r="F265" s="3" t="inlineStr"/>
       <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -6046,15 +7662,25 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
+          <t>8809409345758</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
           <t>MEDIPEEL 24K GOLD SNAIL REPAIR CREAM</t>
         </is>
       </c>
-      <c r="D266" s="3" t="n">
+      <c r="E266" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="E266" s="3" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
+      <c r="F266" s="3" t="inlineStr"/>
       <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>8809409345758 / 8809941827323</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -6067,15 +7693,25 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
+          <t>8809409347004</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
           <t>MEDIPEEL GOLD AGE TOX H8 CREAM</t>
         </is>
       </c>
-      <c r="D267" s="3" t="n">
+      <c r="E267" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E267" s="3" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
+      <c r="F267" s="3" t="inlineStr"/>
       <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>8809409347004 / 8809941827309</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -6088,15 +7724,25 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
+          <t>8809941820270</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
           <t>MEDIPEEL GREEN CICA COLLAGEN CLEAR GEL CLEANSER 2.0</t>
         </is>
       </c>
-      <c r="D268" s="3" t="n">
+      <c r="E268" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E268" s="3" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
+      <c r="F268" s="3" t="inlineStr"/>
       <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>8809409340944 / 8809941820270</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -6109,15 +7755,21 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>8809409346229</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
           <t>MEDI-PEEL DEEP VC ULTRA CREAM</t>
         </is>
       </c>
-      <c r="D269" s="3" t="n">
+      <c r="E269" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="E269" s="3" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
+      <c r="F269" s="3" t="inlineStr"/>
       <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -6130,15 +7782,21 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>8809941823554</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
           <t>MEDI-PEEL LACTO PORE LIFTING MODELING PACK</t>
         </is>
       </c>
-      <c r="D270" s="3" t="n">
+      <c r="E270" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="E270" s="3" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
+      <c r="F270" s="3" t="inlineStr"/>
       <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -6151,15 +7809,21 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>8809941823684</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
           <t>MEDIPEEL LACTO PORE LIFTING PAD 2X</t>
         </is>
       </c>
-      <c r="D271" s="3" t="n">
+      <c r="E271" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E271" s="3" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
+      <c r="F271" s="3" t="inlineStr"/>
       <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -6172,15 +7836,21 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>8809409343082</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
           <t>MEDIPEEL LUXURY 24K GOLD AMPOULE</t>
         </is>
       </c>
-      <c r="D272" s="3" t="n">
+      <c r="E272" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="E272" s="3" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
+      <c r="F272" s="3" t="inlineStr"/>
       <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -6193,15 +7863,25 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
+          <t>8809941825008</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN 3000 SHOT SERUM 2 STEP MASK</t>
         </is>
       </c>
-      <c r="D273" s="3" t="n">
+      <c r="E273" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E273" s="3" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
+      <c r="F273" s="3" t="inlineStr"/>
       <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>8809941825008 / 8809941825060</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -6214,15 +7894,21 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
+          <t>8809409347141</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN DOUBLE TIGHT PAD</t>
         </is>
       </c>
-      <c r="D274" s="3" t="n">
+      <c r="E274" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="E274" s="3" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
+      <c r="F274" s="3" t="inlineStr"/>
       <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -6235,15 +7921,21 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
+          <t>8809409342504</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN WRAPPING MASK</t>
         </is>
       </c>
-      <c r="D275" s="3" t="n">
+      <c r="E275" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E275" s="3" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
+      <c r="F275" s="3" t="inlineStr"/>
       <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -6256,15 +7948,25 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
+          <t>8809941822342</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN BARRIER CREAM</t>
         </is>
       </c>
-      <c r="D276" s="3" t="n">
+      <c r="E276" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="E276" s="3" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
+      <c r="F276" s="3" t="inlineStr"/>
       <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>8809941822342 / 8809941827347</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -6277,15 +7979,21 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
+          <t>8809941825039</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN BRIGHTENING PATCH</t>
         </is>
       </c>
-      <c r="D277" s="3" t="n">
+      <c r="E277" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E277" s="3" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
+      <c r="F277" s="3" t="inlineStr"/>
       <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -6298,15 +8006,21 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
+          <t>8809409340289</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
           <t>RED LACTO COLLAGEN EYE PATCH.</t>
         </is>
       </c>
-      <c r="D278" s="3" t="n">
+      <c r="E278" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E278" s="3" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
+      <c r="F278" s="3" t="inlineStr"/>
       <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -6319,15 +8033,21 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
+          <t>8809409348407</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
           <t>MEDI-PEEL RED LACTO COLLAGEN CLEANSING BALM</t>
         </is>
       </c>
-      <c r="D279" s="3" t="n">
+      <c r="E279" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E279" s="3" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
+      <c r="F279" s="3" t="inlineStr"/>
       <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -6340,15 +8060,25 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
+          <t>8809941821734</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN CLEANSING OIL 2.0</t>
         </is>
       </c>
-      <c r="D280" s="3" t="n">
+      <c r="E280" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E280" s="3" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
+      <c r="F280" s="3" t="inlineStr"/>
       <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>8809941821734 / 8809941826609</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -6361,15 +8091,25 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
+          <t>8809409340975</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN CLEAR FOAM CLEANSER 2.0</t>
         </is>
       </c>
-      <c r="D281" s="3" t="n">
+      <c r="E281" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="E281" s="3" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
+      <c r="F281" s="3" t="inlineStr"/>
       <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>8809409340098 / 8809409340975</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -6382,15 +8122,25 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
+          <t>8809409340098</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN CLEAR FOAM CLEANSER 2.0</t>
         </is>
       </c>
-      <c r="D282" s="3" t="n">
+      <c r="E282" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E282" s="3" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
+      <c r="F282" s="3" t="inlineStr"/>
       <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>8809409340098 / 8809409340975</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -6403,15 +8153,21 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
+          <t>8809941822335</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN TIGHTENING AMPOULE</t>
         </is>
       </c>
-      <c r="D283" s="3" t="n">
+      <c r="E283" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="E283" s="3" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
+      <c r="F283" s="3" t="inlineStr"/>
       <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -6424,15 +8180,21 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
+          <t>8809941825046</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN TROUBLE PATCH</t>
         </is>
       </c>
-      <c r="D284" s="3" t="n">
+      <c r="E284" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="E284" s="3" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
+      <c r="F284" s="3" t="inlineStr"/>
       <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -6445,15 +8207,21 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
+          <t>8809409349534</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
           <t>MEDI-PEEL RED LACTO COLLAGEN PORE LIFTING MASK</t>
         </is>
       </c>
-      <c r="D285" s="3" t="n">
+      <c r="E285" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E285" s="3" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
+      <c r="F285" s="3" t="inlineStr"/>
       <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -6466,15 +8234,21 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
+          <t>8809941824230</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED LACTO COLLAGEN HYDRO GEL CREAM</t>
         </is>
       </c>
-      <c r="D286" s="3" t="n">
+      <c r="E286" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E286" s="3" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
+      <c r="F286" s="3" t="inlineStr"/>
       <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -6487,15 +8261,21 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
+          <t>8809941825022</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
           <t>MEDIPEEL RED CARE PATCH</t>
         </is>
       </c>
-      <c r="D287" s="3" t="n">
+      <c r="E287" s="3" t="n">
         <v>480</v>
       </c>
-      <c r="E287" s="3" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
+      <c r="F287" s="3" t="inlineStr"/>
       <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -6508,15 +8288,25 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
+          <t>8809941827477</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
           <t>MEDIPEEL RETINAL COLLAGEN LIFTING CREAM</t>
         </is>
       </c>
-      <c r="D288" s="3" t="n">
+      <c r="E288" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E288" s="3" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
+      <c r="F288" s="3" t="inlineStr"/>
       <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>8809941826678 / 8809941827477</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -6529,15 +8319,21 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
+          <t>8809409340234</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
           <t>MEDIPEEL RETINOL COLLAGEN LIFTING AMPOULE</t>
         </is>
       </c>
-      <c r="D289" s="3" t="n">
+      <c r="E289" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E289" s="3" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
+      <c r="F289" s="3" t="inlineStr"/>
       <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -6550,15 +8346,25 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
+          <t>8809409345963</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
           <t>MEDIPEEL RETINOL COLLAGEN LIFTING TONER</t>
         </is>
       </c>
-      <c r="D290" s="3" t="n">
+      <c r="E290" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E290" s="3" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
+      <c r="F290" s="3" t="inlineStr"/>
       <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>8809409345963 / 8809941827507</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -6571,15 +8377,21 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
+          <t>8809941821208</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
           <t>MEDI-PEEL RETINOL COLLAGEN LIFTING TRIAL KIT</t>
         </is>
       </c>
-      <c r="D291" s="3" t="n">
+      <c r="E291" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E291" s="3" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
+      <c r="F291" s="3" t="inlineStr"/>
       <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -6592,15 +8404,21 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
+          <t>8809409348445</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
           <t>MEDIPEEL ROYAL ROSE PREMIUM AMPOULE</t>
         </is>
       </c>
-      <c r="D292" s="3" t="n">
+      <c r="E292" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E292" s="3" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
+      <c r="F292" s="3" t="inlineStr"/>
       <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -6613,15 +8431,21 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
+          <t>8809409345437</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
           <t>MEDIPEEL ROSE DIAMOND RADIANT GLOW MASK</t>
         </is>
       </c>
-      <c r="D293" s="3" t="n">
+      <c r="E293" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E293" s="3" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
+      <c r="F293" s="3" t="inlineStr"/>
       <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -6634,15 +8458,21 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
+          <t>8809941825862</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
           <t>MEDIPEEL MELANON X CREAM RX</t>
         </is>
       </c>
-      <c r="D294" s="3" t="n">
+      <c r="E294" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E294" s="3" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
+      <c r="F294" s="3" t="inlineStr"/>
       <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -6655,15 +8485,21 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
+          <t>8809409343020</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
           <t>MEDIPEEL MEZZO FILLA EYE SERUM</t>
         </is>
       </c>
-      <c r="D295" s="3" t="n">
+      <c r="E295" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="E295" s="3" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
+      <c r="F295" s="3" t="inlineStr"/>
       <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -6676,15 +8512,25 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
+          <t>8809409342634</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
           <t>MEDIPEEL MELANON X DROP GEL CREAM</t>
         </is>
       </c>
-      <c r="D296" s="3" t="n">
+      <c r="E296" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E296" s="3" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
+      <c r="F296" s="3" t="inlineStr"/>
       <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>8809409342634 / 8809941827422</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -6697,15 +8543,21 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
+          <t>8809409342566</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
           <t>MEDIPEEL MELANON X CREAM</t>
         </is>
       </c>
-      <c r="D297" s="3" t="n">
+      <c r="E297" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E297" s="3" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
+      <c r="F297" s="3" t="inlineStr"/>
       <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -6718,15 +8570,21 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
+          <t>8809941823714</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
           <t>MEDIPEEL MOOLTOX GLOW MOISTURIZING PAD 2X</t>
         </is>
       </c>
-      <c r="D298" s="3" t="n">
+      <c r="E298" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E298" s="3" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
+      <c r="F298" s="3" t="inlineStr"/>
       <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -6739,15 +8597,21 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
+          <t>8809941824025</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
           <t>MEDIPEEL MOOLTOX PDRN EXOSOME AMPOULE</t>
         </is>
       </c>
-      <c r="D299" s="3" t="n">
+      <c r="E299" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E299" s="3" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
+      <c r="F299" s="3" t="inlineStr"/>
       <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -6760,15 +8624,25 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
+          <t>8809941825954</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
           <t>MEDIPEEL MOOLTOX PDRN HYAL DROP GEL CREAM</t>
         </is>
       </c>
-      <c r="D300" s="3" t="n">
+      <c r="E300" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E300" s="3" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
+      <c r="F300" s="3" t="inlineStr"/>
       <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>8809941825954 / 8809941827057</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -6781,15 +8655,21 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
+          <t>8809941825190</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
           <t>MEDIPEEL VEGAN PDRN HYAL MOISTURE MASK</t>
         </is>
       </c>
-      <c r="D301" s="3" t="n">
+      <c r="E301" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E301" s="3" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" s="3" t="inlineStr"/>
       <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -6802,15 +8682,21 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
+          <t>8809409348315</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
           <t>MEDIPEEL BIO INTENSE GLUTATHIONE WHITE SILKY TONER</t>
         </is>
       </c>
-      <c r="D302" s="3" t="n">
+      <c r="E302" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="E302" s="3" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
+      <c r="F302" s="3" t="inlineStr"/>
       <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -6823,15 +8709,25 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
+          <t>8809941823158</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
           <t>MEDIPEEL BIO INTENSE GLUTATHIONE WHITE AMPOULE 2.0</t>
         </is>
       </c>
-      <c r="D303" s="3" t="n">
+      <c r="E303" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="E303" s="3" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" s="3" t="inlineStr"/>
       <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>8809941823158 / 8809941826708</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -6844,15 +8740,25 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
+          <t>8809409347462</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
           <t>MEDIPEEL BIO INTENSE GLUTATHIONE WHITE CREAM</t>
         </is>
       </c>
-      <c r="D304" s="3" t="n">
+      <c r="E304" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E304" s="3" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
+      <c r="F304" s="3" t="inlineStr"/>
       <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>8809409347462 / 8809941827538</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -6865,15 +8771,21 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
+          <t>8809941821055</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
           <t>MEDIPEEL VEGAN VITAMIN COLLAGEN WRAPPING MASK.</t>
         </is>
       </c>
-      <c r="D305" s="3" t="n">
+      <c r="E305" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E305" s="3" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" s="3" t="inlineStr"/>
       <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -6886,15 +8798,21 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
+          <t>8809941821383</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
           <t>MEDI-PEEL VEGAN VITAMIN COLLAGEN CLEAR GEL CLEANSER</t>
         </is>
       </c>
-      <c r="D306" s="3" t="n">
+      <c r="E306" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E306" s="3" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
+      <c r="F306" s="3" t="inlineStr"/>
       <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -6907,15 +8825,25 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
+          <t>8809941820690</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
           <t>MEDIPEEL VEGAN VITAMIN COLLAGEN CLEAR GEL CLEANSER.</t>
         </is>
       </c>
-      <c r="D307" s="3" t="n">
+      <c r="E307" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E307" s="3" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
+      <c r="F307" s="3" t="inlineStr"/>
       <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>8809941820690 / 8809941820706</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -6928,15 +8856,21 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
+          <t>8809941823707</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
           <t>MEDIPEEL VITAMIN MELA TONING PAD 2X</t>
         </is>
       </c>
-      <c r="D308" s="3" t="n">
+      <c r="E308" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E308" s="3" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
+      <c r="F308" s="3" t="inlineStr"/>
       <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -6949,15 +8883,21 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
+          <t>8809409345383</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
           <t>MEDIPEEL VITAMIN BOMB REFRESHING MASK</t>
         </is>
       </c>
-      <c r="D309" s="3" t="n">
+      <c r="E309" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E309" s="3" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
+      <c r="F309" s="3" t="inlineStr"/>
       <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -6970,15 +8910,21 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
+          <t>8809941823646</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
           <t>MEDI-PEEL CELL TOXING DERMAJOURS BLACK TRUFFLE REPAIR MASK</t>
         </is>
       </c>
-      <c r="D310" s="3" t="n">
+      <c r="E310" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E310" s="3" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
+      <c r="F310" s="3" t="inlineStr"/>
       <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -6991,15 +8937,21 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
+          <t>8809409343709</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
           <t>MEDIPEEL CELL TOXING DERMAJOURS EYE CREAM</t>
         </is>
       </c>
-      <c r="D311" s="3" t="n">
+      <c r="E311" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E311" s="3" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
+      <c r="F311" s="3" t="inlineStr"/>
       <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -7012,15 +8964,25 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
+          <t>8809409345901</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
           <t>MEDIPEEL CELL TOXING DERMAJOURS AMPOULE</t>
         </is>
       </c>
-      <c r="D312" s="3" t="n">
+      <c r="E312" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E312" s="3" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
+      <c r="F312" s="3" t="inlineStr"/>
       <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>8809409345901 / 8809941827408</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -7033,15 +8995,21 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
+          <t>8809409346809</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
           <t>MEDI-PEEL CELL TOXING DERMAJOURS EMULSION</t>
         </is>
       </c>
-      <c r="D313" s="3" t="n">
+      <c r="E313" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E313" s="3" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
+      <c r="F313" s="3" t="inlineStr"/>
       <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -7054,15 +9022,21 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
+          <t>8809409346786</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
           <t>MEDIPEEL CELL TOXING DERMAJOURS ESSENCIAL SET</t>
         </is>
       </c>
-      <c r="D314" s="3" t="n">
+      <c r="E314" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E314" s="3" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
+      <c r="F314" s="3" t="inlineStr"/>
       <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -7075,15 +9049,25 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
+          <t>8809941827378</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
           <t>MEDIPEEL CELL TOXING DERMAJOURS CREAM</t>
         </is>
       </c>
-      <c r="D315" s="3" t="n">
+      <c r="E315" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E315" s="3" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
+      <c r="F315" s="3" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>8809409345895 / 8809941827378</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -7096,15 +9080,21 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
+          <t>8809409346793</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
           <t>MEDI-PEEL CELL TOXING DERMAJOURS TONER</t>
         </is>
       </c>
-      <c r="D316" s="3" t="n">
+      <c r="E316" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E316" s="3" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" s="3" t="inlineStr"/>
       <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -7117,15 +9107,25 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
+          <t>8809409340432</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
           <t>MEDIPEEL EYE TOX CREAM</t>
         </is>
       </c>
-      <c r="D317" s="3" t="n">
+      <c r="E317" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="E317" s="3" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
+      <c r="F317" s="3" t="inlineStr"/>
       <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>8809409340432 / 8809941827491</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -7138,15 +9138,21 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
+          <t>8809409346441</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
           <t>MEDI-PEEL AQUA MOOLTOX SPARKLING PAD</t>
         </is>
       </c>
-      <c r="D318" s="3" t="n">
+      <c r="E318" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="E318" s="3" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
+      <c r="F318" s="3" t="inlineStr"/>
       <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -7159,15 +9165,21 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
+          <t>8809409348667</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
           <t>AHA+ BHA 28 DAYS HYAL CREAM 28-DAYS SKIN RECOVERY SOLUTION</t>
         </is>
       </c>
-      <c r="D319" s="3" t="n">
+      <c r="E319" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="E319" s="3" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
+      <c r="F319" s="3" t="inlineStr"/>
       <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -7180,15 +9192,25 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
+          <t>8809941827095</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
           <t>MEDIPEEL ALGO-TOX DEEP CLEAR</t>
         </is>
       </c>
-      <c r="D320" s="3" t="n">
+      <c r="E320" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="E320" s="3" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
+      <c r="F320" s="3" t="inlineStr"/>
       <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>8809409342887 / 8809941827095</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -7201,15 +9223,21 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
+          <t>8809941820997</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
           <t>MEDI-PEEL ALGO-TOX VITA CLEANSER</t>
         </is>
       </c>
-      <c r="D321" s="3" t="n">
+      <c r="E321" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="E321" s="3" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
+      <c r="F321" s="3" t="inlineStr"/>
       <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -7222,15 +9250,21 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
+          <t>8809941820324</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
           <t>MEDI-PEEL EAZY FILLER AMPOULE</t>
         </is>
       </c>
-      <c r="D322" s="3" t="n">
+      <c r="E322" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="E322" s="3" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
+      <c r="F322" s="3" t="inlineStr"/>
       <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -7243,15 +9277,21 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
+          <t>8809941820331</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
           <t>MEDIPEEL EAZY FILLER CREAM</t>
         </is>
       </c>
-      <c r="D323" s="3" t="n">
+      <c r="E323" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E323" s="3" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
+      <c r="F323" s="3" t="inlineStr"/>
       <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -7264,15 +9304,21 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
+          <t>8809409342382</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
           <t>COLLAGEN SUPER 10 SLEEPING CREAM</t>
         </is>
       </c>
-      <c r="D324" s="3" t="n">
+      <c r="E324" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E324" s="3" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
+      <c r="F324" s="3" t="inlineStr"/>
       <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -7285,15 +9331,25 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
+          <t>8809409346656</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
           <t>MEDIPEEL POWER AQUA CREAM</t>
         </is>
       </c>
-      <c r="D325" s="3" t="n">
+      <c r="E325" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E325" s="3" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
+      <c r="F325" s="3" t="inlineStr"/>
       <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>8809409346656 / 8809941827187</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -7306,15 +9362,21 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
+          <t>8809409348230</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 MELA STICK</t>
         </is>
       </c>
-      <c r="D326" s="3" t="n">
+      <c r="E326" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E326" s="3" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
+      <c r="F326" s="3" t="inlineStr"/>
       <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -7327,15 +9389,21 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
+          <t>8809941820393</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
           <t>MEDI-PEEL PEPTIDE 9 BIO SUN STICK PRO SPF 50+ PA ++++</t>
         </is>
       </c>
-      <c r="D327" s="3" t="n">
+      <c r="E327" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E327" s="3" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
+      <c r="F327" s="3" t="inlineStr"/>
       <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -7348,15 +9416,25 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
+          <t>8809941826531</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VOLUME LIF-TOX EYE CREAM</t>
         </is>
       </c>
-      <c r="D328" s="3" t="n">
+      <c r="E328" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="E328" s="3" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
+      <c r="F328" s="3" t="inlineStr"/>
       <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>8809409340319 / 8809941826531</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -7369,15 +9447,25 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
+          <t>8809941821802</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VOLUME LIFTING ALL IN ONE ESSENCE PRO</t>
         </is>
       </c>
-      <c r="D329" s="3" t="n">
+      <c r="E329" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E329" s="3" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
+      <c r="F329" s="3" t="inlineStr"/>
       <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>8809941821802 / 8809941827170</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -7390,15 +9478,21 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
+          <t>8809941821512</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
           <t>MEDI-PEEL PEPTIDE 9 VOLUME LIFTING ALL IN ONE PODOAMPOULE PRO</t>
         </is>
       </c>
-      <c r="D330" s="3" t="n">
+      <c r="E330" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E330" s="3" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
+      <c r="F330" s="3" t="inlineStr"/>
       <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -7411,15 +9505,25 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
+          <t>8809941820386</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VOLUME ALL IN ONE ESSENCE PRO</t>
         </is>
       </c>
-      <c r="D331" s="3" t="n">
+      <c r="E331" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E331" s="3" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
+      <c r="F331" s="3" t="inlineStr"/>
       <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>8809941820386 / 8809941827163</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -7432,15 +9536,25 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
+          <t>8809941820416</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VOLUME WHITE CICA ESSENCE PRO</t>
         </is>
       </c>
-      <c r="D332" s="3" t="n">
+      <c r="E332" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E332" s="3" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
+      <c r="F332" s="3" t="inlineStr"/>
       <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>8809941820416 / 8809941827248</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -7453,15 +9567,25 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
+          <t>8809941822243</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VITANOL AMPOULE PRO</t>
         </is>
       </c>
-      <c r="D333" s="3" t="n">
+      <c r="E333" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E333" s="3" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
+      <c r="F333" s="3" t="inlineStr"/>
       <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>8809941822243 / 8809941827453</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -7474,15 +9598,25 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
+          <t>8809941827460</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VITANOL CREAM PRO</t>
         </is>
       </c>
-      <c r="D334" s="3" t="n">
+      <c r="E334" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E334" s="3" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
+      <c r="F334" s="3" t="inlineStr"/>
       <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>8809941822236 / 8809941827460</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -7495,15 +9629,21 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
+          <t>8809941820423</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
           <t>MEDI-PEEL PEPTIDE 9 AQUA VOLUME TOX MIST PRO</t>
         </is>
       </c>
-      <c r="D335" s="3" t="n">
+      <c r="E335" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="E335" s="3" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
+      <c r="F335" s="3" t="inlineStr"/>
       <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -7516,15 +9656,25 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
+          <t>8809941826494</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 AQUA ESSENCE LIFTING EYE CREAM</t>
         </is>
       </c>
-      <c r="D336" s="3" t="n">
+      <c r="E336" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E336" s="3" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
+      <c r="F336" s="3" t="inlineStr"/>
       <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>8809409341422 / 8809941826494</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -7537,15 +9687,25 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
+          <t>8809409341347</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 AQUA ESSENCE LIFTING AMPOULE</t>
         </is>
       </c>
-      <c r="D337" s="3" t="n">
+      <c r="E337" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E337" s="3" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
+      <c r="F337" s="3" t="inlineStr"/>
       <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>8809409341347 / 8809941826470</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -7558,15 +9718,25 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
+          <t>8809941826449</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 AQUA ESSENCE EMULSION</t>
         </is>
       </c>
-      <c r="D338" s="3" t="n">
+      <c r="E338" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E338" s="3" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
+      <c r="F338" s="3" t="inlineStr"/>
       <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>8809409344683 / 8809941826449</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -7579,15 +9749,25 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
+          <t>8809941826432</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 AQUA ESSENCE TONER</t>
         </is>
       </c>
-      <c r="D339" s="3" t="n">
+      <c r="E339" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E339" s="3" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
+      <c r="F339" s="3" t="inlineStr"/>
       <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>8809409344676 / 8809941826432</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -7600,15 +9780,21 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
+          <t>8809409341392</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
           <t>MEDI-PEEL PEPTIDE 9 AQUA ESSENCE FACIAL CLEANSER</t>
         </is>
       </c>
-      <c r="D340" s="3" t="n">
+      <c r="E340" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E340" s="3" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
+      <c r="F340" s="3" t="inlineStr"/>
       <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -7621,15 +9807,21 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
+          <t>8809409345116</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 PREMIUM SKINCARE SET</t>
         </is>
       </c>
-      <c r="D341" s="3" t="n">
+      <c r="E341" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E341" s="3" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
+      <c r="F341" s="3" t="inlineStr"/>
       <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -7642,15 +9834,25 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
+          <t>8809941827484</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 HYALURONIC VOLUMY EYE CREAM</t>
         </is>
       </c>
-      <c r="D342" s="3" t="n">
+      <c r="E342" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="E342" s="3" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
+      <c r="F342" s="3" t="inlineStr"/>
       <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>8809409343327 / 8809941827484</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -7663,15 +9865,25 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
+          <t>8809941827224</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE 9 VOLUME TOX CREAM PRO</t>
         </is>
       </c>
-      <c r="D343" s="3" t="n">
+      <c r="E343" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E343" s="3" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
+      <c r="F343" s="3" t="inlineStr"/>
       <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>8809941820447 / 8809941827224</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -7684,15 +9896,21 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
+          <t>8809409348254</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
           <t>MEDI-PEEL PEPTIDE-TOX BOR WRINKLE STICK</t>
         </is>
       </c>
-      <c r="D344" s="3" t="n">
+      <c r="E344" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E344" s="3" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
+      <c r="F344" s="3" t="inlineStr"/>
       <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -7705,15 +9923,25 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
+          <t>8809409349961</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE-TOX BOR EYE CREAM</t>
         </is>
       </c>
-      <c r="D345" s="3" t="n">
+      <c r="E345" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E345" s="3" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
+      <c r="F345" s="3" t="inlineStr"/>
       <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>8809409349961 / 8809941827385</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -7726,15 +9954,25 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
+          <t>8809409341705</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE-TOX BOR AMPOULE</t>
         </is>
       </c>
-      <c r="D346" s="3" t="n">
+      <c r="E346" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="E346" s="3" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
+      <c r="F346" s="3" t="inlineStr"/>
       <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>8809409341705 / 8809941827354</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -7747,15 +9985,21 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
+          <t>8809941822229</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
           <t>MEDI-PEEL PEPTIDE-TOX BOR AMPOULE OIL</t>
         </is>
       </c>
-      <c r="D347" s="3" t="n">
+      <c r="E347" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E347" s="3" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
+      <c r="F347" s="3" t="inlineStr"/>
       <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -7768,15 +10012,25 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
+          <t>8809409347455</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE-TOX BOR CREAM</t>
         </is>
       </c>
-      <c r="D348" s="3" t="n">
+      <c r="E348" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E348" s="3" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" s="3" t="inlineStr"/>
       <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>8809409347455 / 8809409347578 / 8809941827361</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -7789,15 +10043,25 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
+          <t>8809409348308</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
           <t>MEDIPEEL PEPTIDE-TOX BOR TONER</t>
         </is>
       </c>
-      <c r="D349" s="3" t="n">
+      <c r="E349" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="E349" s="3" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
+      <c r="F349" s="3" t="inlineStr"/>
       <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>8809409348308 / 8809941827392</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -7810,15 +10074,25 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
+          <t>8809941822168</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
           <t>MEDIPEEL PREMIUM GOLDEN CAMELLIA WRINKLE ESSENCE</t>
         </is>
       </c>
-      <c r="D350" s="3" t="n">
+      <c r="E350" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E350" s="3" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
+      <c r="F350" s="3" t="inlineStr"/>
       <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>8809941822168 / 8809941827132</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -7831,15 +10105,25 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
+          <t>8809941822175</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
           <t>MEDIPEEL PREMIUM GOLDEN CAMELLIA WRINKLE CREAM</t>
         </is>
       </c>
-      <c r="D351" s="3" t="n">
+      <c r="E351" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E351" s="3" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
+      <c r="F351" s="3" t="inlineStr"/>
       <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>8809941822175 / 8809941827149</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -7852,15 +10136,21 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
+          <t>8809941826234</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
           <t>MEDIPEEL PREMIUM COLLAGEN NAITE 1500 SHOT NECK PATCH 1.0</t>
         </is>
       </c>
-      <c r="D352" s="3" t="n">
+      <c r="E352" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E352" s="3" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
+      <c r="F352" s="3" t="inlineStr"/>
       <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -7873,15 +10163,25 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
+          <t>8809941825688</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
           <t>MEDIPEEL PREMIUM COLLAGEN NAITE THREAD NECK CREAM 3.0</t>
         </is>
       </c>
-      <c r="D353" s="3" t="n">
+      <c r="E353" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E353" s="3" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
+      <c r="F353" s="3" t="inlineStr"/>
       <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>8809941825688 / 8809941826944</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -7894,15 +10194,25 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
+          <t>8809941824995</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO CICA-NOL B5 3000 SHOT SERUM 2 STEP MASK.</t>
         </is>
       </c>
-      <c r="D354" s="3" t="n">
+      <c r="E354" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E354" s="3" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
+      <c r="F354" s="3" t="inlineStr"/>
       <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>8809941824995 / 8809941825053</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -7915,15 +10225,21 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
+          <t>8809941822373</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO CICA-NOL B5 CALMING VEGAN WRAPPING MASK</t>
         </is>
       </c>
-      <c r="D355" s="3" t="n">
+      <c r="E355" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E355" s="3" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
+      <c r="F355" s="3" t="inlineStr"/>
       <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -7936,15 +10252,21 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
+          <t>8809409348322</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
           <t>MEDIPEEL PHYTO CICA-NOL CREAM</t>
         </is>
       </c>
-      <c r="D356" s="3" t="n">
+      <c r="E356" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E356" s="3" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
+      <c r="F356" s="3" t="inlineStr"/>
       <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -7957,15 +10279,21 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
+          <t>8809941820454</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
           <t>MEDIPEEL HERBAL PEEL TOX PRO</t>
         </is>
       </c>
-      <c r="D357" s="3" t="n">
+      <c r="E357" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E357" s="3" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
+      <c r="F357" s="3" t="inlineStr"/>
       <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -7978,15 +10306,21 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
+          <t>8809409343747</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
           <t>HYALURON ROSE ENERGY TOX AMPOULE MASK 2X</t>
         </is>
       </c>
-      <c r="D358" s="3" t="n">
+      <c r="E358" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E358" s="3" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
+      <c r="F358" s="3" t="inlineStr"/>
       <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -7999,15 +10333,25 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
+          <t>8809941827071</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
           <t>MEDIPEEL HYALURON DARK BENONE PEPTIDE 9 AMPOULE EYE PATCH</t>
         </is>
       </c>
-      <c r="D359" s="3" t="n">
+      <c r="E359" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E359" s="3" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
+      <c r="F359" s="3" t="inlineStr"/>
       <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>8809409343655 / 8809941827071</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -8020,15 +10364,21 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
+          <t>8809409343631</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
           <t>MEDI-PEEL HYALURON ROSE PEPTIDE 9 AMPOULE EYE PATCH</t>
         </is>
       </c>
-      <c r="D360" s="3" t="n">
+      <c r="E360" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E360" s="3" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
+      <c r="F360" s="3" t="inlineStr"/>
       <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -8041,15 +10391,25 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
+          <t>8809409343648</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
           <t>MEDIPEEL HYALURON CICA PEPTIDE 9 AMPOULE EYE PATCH</t>
         </is>
       </c>
-      <c r="D361" s="3" t="n">
+      <c r="E361" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E361" s="3" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
+      <c r="F361" s="3" t="inlineStr"/>
       <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>8809409343648 / 8809941827088</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -8062,15 +10422,25 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
+          <t>8809409343662</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
           <t>MEDIPEEL HYALURON AQUA PEPTIDE 9 AMPOULE EYE PATCH</t>
         </is>
       </c>
-      <c r="D362" s="3" t="n">
+      <c r="E362" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="E362" s="3" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
+      <c r="F362" s="3" t="inlineStr"/>
       <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>8809409343662 / 8809941826463</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -8083,15 +10453,25 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
+          <t>8809941827262</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
           <t>MEDIPEEL HYAL KOMBUCHA TEA-TOX AMPOULE</t>
         </is>
       </c>
-      <c r="D363" s="3" t="n">
+      <c r="E363" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E363" s="3" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
+      <c r="F363" s="3" t="inlineStr"/>
       <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>8809409346458 / 8809941827262</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -8104,15 +10484,25 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
+          <t>8809941827217</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
           <t>MEDIPEEL HYAL KOMBUCHA TEA-TOX CREAM</t>
         </is>
       </c>
-      <c r="D364" s="3" t="n">
+      <c r="E364" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="E364" s="3" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
+      <c r="F364" s="3" t="inlineStr"/>
       <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>8809409346489 / 8809941827217</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -8125,15 +10515,25 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
+          <t>8809941827200</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
           <t>MEDIPEEL HYAL KOMBUCHA TEA-TOX TONER</t>
         </is>
       </c>
-      <c r="D365" s="3" t="n">
+      <c r="E365" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E365" s="3" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
+      <c r="F365" s="3" t="inlineStr"/>
       <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>8809409342474 / 8809941827200</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -8146,15 +10546,21 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
+          <t>8809668028041</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
           <t>ET Baking Powder BB Deep Foam 160g(21AD)</t>
         </is>
       </c>
-      <c r="D366" s="3" t="n">
+      <c r="E366" s="3" t="n">
         <v>2880</v>
       </c>
-      <c r="E366" s="3" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
+      <c r="F366" s="3" t="inlineStr"/>
       <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -8167,15 +10573,21 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
+          <t>8809668028058</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
           <t>ET Baking Powder BB Deep Foam 30g(21AD)</t>
         </is>
       </c>
-      <c r="D367" s="3" t="n">
+      <c r="E367" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="E367" s="3" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
+      <c r="F367" s="3" t="inlineStr"/>
       <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -8188,15 +10600,21 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
+          <t>8809668028089</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
           <t>ET.Baking Powder Pore Foam 160g (21AD)</t>
         </is>
       </c>
-      <c r="D368" s="3" t="n">
+      <c r="E368" s="3" t="n">
         <v>2880</v>
       </c>
-      <c r="E368" s="3" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
+      <c r="F368" s="3" t="inlineStr"/>
       <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -8209,15 +10627,21 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
+          <t>8809820698891</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
           <t>ET.Baking.P C. P. Scrub 7g*24ea(23')</t>
         </is>
       </c>
-      <c r="D369" s="3" t="n">
+      <c r="E369" s="3" t="n">
         <v>2400</v>
       </c>
-      <c r="E369" s="3" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
+      <c r="F369" s="3" t="inlineStr"/>
       <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -8230,15 +10654,21 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
+          <t>8809685797173</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [BERRY] 20g</t>
         </is>
       </c>
-      <c r="D370" s="3" t="n">
+      <c r="E370" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E370" s="3" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
+      <c r="F370" s="3" t="inlineStr"/>
       <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -8251,15 +10681,21 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
+          <t>8809685797357</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [GRAPEFRUIT] 20g</t>
         </is>
       </c>
-      <c r="D371" s="3" t="n">
+      <c r="E371" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E371" s="3" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
+      <c r="F371" s="3" t="inlineStr"/>
       <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -8272,15 +10708,21 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
+          <t>8809685797371</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [APPLE LIME] 20g</t>
         </is>
       </c>
-      <c r="D372" s="3" t="n">
+      <c r="E372" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E372" s="3" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
+      <c r="F372" s="3" t="inlineStr"/>
       <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -8293,15 +10735,21 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
+          <t>8809685797395</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [MINT CHOCO] 20g</t>
         </is>
       </c>
-      <c r="D373" s="3" t="n">
+      <c r="E373" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E373" s="3" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
+      <c r="F373" s="3" t="inlineStr"/>
       <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -8314,15 +10762,21 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
+          <t>8809925203808</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [VANILLA] 20g</t>
         </is>
       </c>
-      <c r="D374" s="3" t="n">
+      <c r="E374" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E374" s="3" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
+      <c r="F374" s="3" t="inlineStr"/>
       <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -8335,15 +10789,21 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
+          <t>8809925206410</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [MANGO] 20g</t>
         </is>
       </c>
-      <c r="D375" s="3" t="n">
+      <c r="E375" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E375" s="3" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
+      <c r="F375" s="3" t="inlineStr"/>
       <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -8356,15 +10816,21 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
+          <t>8809925206427</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [GUMMY BEAR] 20g</t>
         </is>
       </c>
-      <c r="D376" s="3" t="n">
+      <c r="E376" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E376" s="3" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
+      <c r="F376" s="3" t="inlineStr"/>
       <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -8377,15 +10843,21 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
+          <t>8809925206433</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [SWEET CANDY] 20g</t>
         </is>
       </c>
-      <c r="D377" s="3" t="n">
+      <c r="E377" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E377" s="3" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
+      <c r="F377" s="3" t="inlineStr"/>
       <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -8398,15 +10870,21 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
+          <t>8809925206441</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [PEACH ICED TEA] 20g</t>
         </is>
       </c>
-      <c r="D378" s="3" t="n">
+      <c r="E378" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E378" s="3" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
+      <c r="F378" s="3" t="inlineStr"/>
       <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -8419,15 +10897,21 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
+          <t>8800283633894</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
           <t>LIP SLEEPING MASK EX [Strawberry cake] 20g</t>
         </is>
       </c>
-      <c r="D379" s="3" t="n">
+      <c r="E379" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E379" s="3" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
+      <c r="F379" s="3" t="inlineStr"/>
       <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -8438,17 +10922,19 @@
           <t>Laneige</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
         <is>
           <t>LIP SLEEPING MASK EX [BERRY] 3g</t>
         </is>
       </c>
-      <c r="D380" s="3" t="n">
+      <c r="E380" s="3" t="n">
         <v>3000</v>
       </c>
-      <c r="E380" s="3" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
+      <c r="F380" s="3" t="inlineStr"/>
       <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -8459,17 +10945,19 @@
           <t>Laneige</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
         <is>
           <t>LIP SLEEPING MASK EX [GUMMY BEAR] 3g</t>
         </is>
       </c>
-      <c r="D381" s="3" t="n">
+      <c r="E381" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E381" s="3" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
+      <c r="F381" s="3" t="inlineStr"/>
       <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -8480,17 +10968,19 @@
           <t>Laneige</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
         <is>
           <t>LIP SLEEPING MASK EX [SWEET CANDY] 3g</t>
         </is>
       </c>
-      <c r="D382" s="3" t="n">
+      <c r="E382" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E382" s="3" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
+      <c r="F382" s="3" t="inlineStr"/>
       <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -8501,17 +10991,19 @@
           <t>Laneige</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
         <is>
           <t>LIP SLEEPING MASK EX [MANGO] 3g</t>
         </is>
       </c>
-      <c r="D383" s="3" t="n">
+      <c r="E383" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E383" s="3" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
+      <c r="F383" s="3" t="inlineStr"/>
       <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="4" t="inlineStr"/>
@@ -8521,12 +11013,14 @@
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr"/>
-      <c r="D384" s="5" t="n">
+      <c r="D384" s="4" t="inlineStr"/>
+      <c r="E384" s="5" t="n">
         <v>88361</v>
       </c>
-      <c r="E384" s="5" t="inlineStr"/>
-      <c r="F384" s="4" t="inlineStr"/>
+      <c r="F384" s="5" t="inlineStr"/>
       <c r="G384" s="4" t="inlineStr"/>
+      <c r="H384" s="4" t="inlineStr"/>
+      <c r="I384" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
